--- a/ワードプレス全体図.xlsx
+++ b/ワードプレス全体図.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A39D12C-74F0-4BA3-9E2A-5299FA1942DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D6D1BE-7E17-40A1-B2A0-EA9035D3A311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="0" windowWidth="21660" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="630" yWindow="900" windowWidth="17580" windowHeight="12630" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="archive.php" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="77">
   <si>
     <t>。ｐｈ</t>
   </si>
@@ -31,13 +31,7 @@
     <t>管理画面からの登録</t>
   </si>
   <si>
-    <t>archive.php</t>
-  </si>
-  <si>
     <t>〇</t>
-  </si>
-  <si>
-    <t>single.php</t>
   </si>
   <si>
     <t>archive〇〇.php、</t>
@@ -980,12 +974,49 @@
     <t>お知らせ	投稿タイプの名前（グループ名みたいなもの</t>
     <phoneticPr fontId="7"/>
   </si>
+  <si>
+    <t>カスタムフィールドリンク</t>
+  </si>
+  <si>
+    <t>archive.php
+（一覧を表示するページを作成）</t>
+    <rPh sb="13" eb="15">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>single.php
+一覧の特定の記事をクリックした後の画面</t>
+    <rPh sb="11" eb="13">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1088,6 +1119,12 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1211,7 +1248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1264,9 +1301,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1287,6 +1321,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1374,7 +1412,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1423,7 +1461,7 @@
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B9324D-2C05-46F4-A756-E64ABED0DE4D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1473,7 +1511,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32A4C381-A785-0F10-3C7B-A939FA719087}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1517,7 +1555,7 @@
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C10E96A3-320D-54C7-6681-86A74A3397BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1561,7 +1599,7 @@
         <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2C7711B-F448-770D-A786-4C9FD3DD242B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1605,7 +1643,7 @@
         <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DA5E81B-9DC9-65FD-C838-73D298BF53A3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1649,7 +1687,7 @@
         <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADDD094D-2448-66DA-8F73-5D2D3B095E27}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1693,7 +1731,7 @@
         <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB7F6EC-F078-CF00-7837-643893E520F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1737,7 +1775,7 @@
         <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78EB8EFB-4540-CCC5-50DA-BFB2EB5F597A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1781,7 +1819,7 @@
         <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E1E1245-79C6-445B-F256-8CA52EBF64D5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1825,7 +1863,7 @@
         <xdr:cNvPr id="11" name="図 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAF5C7C0-CC78-BA06-D9A4-FFDDEF87BC86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2227,97 +2265,97 @@
   <sheetData>
     <row r="1" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="338.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" ht="338.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="4" t="s">
+      <c r="E3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="180" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="E4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="180" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>10</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G6" s="8"/>
     </row>
     <row r="8" spans="2:8" ht="176.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D8" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8" s="10"/>
     </row>
@@ -2338,15 +2376,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB694F7D-8D9F-4AD4-8E29-C2A9151A90F7}">
-  <dimension ref="B2:G2"/>
+  <dimension ref="B2:G30"/>
   <sheetFormatPr defaultColWidth="6.25" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="25" t="s">
         <v>74</v>
-      </c>
-      <c r="G2" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2371,327 +2414,287 @@
   <sheetData>
     <row r="1" spans="3:10" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C1" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="H2" s="16"/>
-      <c r="J2" s="23" t="s">
-        <v>50</v>
+      <c r="J2" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="19"/>
-      <c r="J3" s="24" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="H3" s="18"/>
+      <c r="J3" s="23" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19"/>
-      <c r="J4" s="24" t="s">
-        <v>49</v>
+        <v>54</v>
+      </c>
+      <c r="H4" s="18"/>
+      <c r="J4" s="23" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
+        <v>55</v>
+      </c>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="19"/>
+        <v>58</v>
+      </c>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+        <v>56</v>
+      </c>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C8" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+        <v>57</v>
+      </c>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
+      <c r="C10" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+        <v>61</v>
+      </c>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+        <v>45</v>
+      </c>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="3:10" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C13" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="22"/>
+      <c r="C13" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" spans="3:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C65" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C66" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C67" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C68" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C75" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="120" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="128" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="129" spans="3:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="130" spans="3:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131" spans="3:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="132" spans="3:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C132" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="3:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="3:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="135" spans="3:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144" spans="3:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C144" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C145" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="146" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C146" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="147" spans="3:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C147" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
